--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:23:16+00:00</t>
+    <t>2026-08-10T12:51:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -487,7 +487,7 @@
     <t>システムが管理する、施設内で診断レポートを一意に識別するためのID【詳細参照】</t>
   </si>
   <si>
-    <t>システムが管理する、施設内で診断レポートを一意に識別するためのID</t>
+    <t>システムが管理する、施設内で診断レポートを一意に識別するためのID。</t>
   </si>
   <si>
     <t>病理では標本番号（受付番号、病理番号）＋版数を指定する。</t>
@@ -515,14 +515,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
     <t>他のシステムから依頼されたオーダ情報【詳細参照】</t>
   </si>
   <si>
-    <t>他のシステムから依頼されたオーダ情報</t>
+    <t>他のシステムから依頼されたオーダ情報。</t>
   </si>
   <si>
     <t>通常、依頼元となるServiceRequestリソースを参照する。他のシステムと連携していない場合は参照不要。</t>
@@ -546,7 +546,7 @@
     <t>診断レポートのステータス【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートのステータス</t>
+    <t>診断レポートのステータス。</t>
   </si>
   <si>
     <t>preliminary（中間）|final（確定済、承認済）|appended（追加）|amended（修正）|corrected（訂正）</t>
@@ -590,7 +590,7 @@
     <t>診断レポートの分野を表すコード【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートの分野を表すコード</t>
+    <t>診断レポートの分野を表すコード。</t>
   </si>
   <si>
     <t>Value Set：JPCore_DiagnosticReport_Categoryの中から「LP7839-6」（Pathology（病理））を指定する。</t>
@@ -624,7 +624,7 @@
     <t>病理分野の診断レポートを分類するためのコード【詳細参照】</t>
   </si>
   <si>
-    <t>病理分野の診断レポートを分類するためのコード</t>
+    <t>病理分野の診断レポートを分類するためのコード。</t>
   </si>
   <si>
     <t>Value Set：JPCore_DocumentCodeの中から適切な病理分野の報告書のコードを指定する。例：組織診は「11526-1」（病理検査報告書）、細胞診は「47526-9」（細胞診報告書）、剖検は「18743-5」（剖検報告書）を指定する。</t>
@@ -662,7 +662,7 @@
     <t>診断レポートの対象患者に関する情報【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートの対象患者に関する情報</t>
+    <t>診断レポートの対象患者に関する情報。</t>
   </si>
   <si>
     <t>JP Core Patientリソースを参照する。</t>
@@ -697,7 +697,7 @@
     <t>この診断レポートを書くきっかけとなった情報【詳細参照】</t>
   </si>
   <si>
-    <t>この診断レポートを書くきっかけとなった情報</t>
+    <t>この診断レポートを書くきっかけとなった情報。</t>
   </si>
   <si>
     <t>JP Core Encounterリソースを参照する。</t>
@@ -732,7 +732,7 @@
     <t>診断レポートの作成日時【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートの作成日時</t>
+    <t>診断レポートの作成日時。</t>
   </si>
   <si>
     <t>DateTimeを採用する。</t>
@@ -767,7 +767,7 @@
     <t>レポート確定日時【詳細参照】</t>
   </si>
   <si>
-    <t>レポート確定日時</t>
+    <t>レポート確定日時。</t>
   </si>
   <si>
     <t>StatusがFinalになった日時を指定する。</t>
@@ -796,7 +796,7 @@
 </t>
   </si>
   <si>
-    <t>レポートを確定した医師</t>
+    <t>レポートを確定した医師。</t>
   </si>
   <si>
     <t>これは、必ずしもアトミックデータ項目または結果を解釈したエンティティのソースではありません。臨床報告に責任を負うのはエンティティです。 / This is not necessarily the source of the atomic data items or the entity that interpreted the results. It is the entity that takes responsibility for the clinical report.</t>
@@ -827,7 +827,7 @@
     <t>この診断レポートの作成者【詳細参照】</t>
   </si>
   <si>
-    <t>この診断レポートの作成者</t>
+    <t>この診断レポートの作成者。</t>
   </si>
   <si>
     <t>複数いる場合は、列記する。</t>
@@ -846,7 +846,7 @@
     <t>この診断レポートの検体に関する情報【詳細参照】</t>
   </si>
   <si>
-    <t>この診断レポートの検体に関する情報</t>
+    <t>この診断レポートの検体に関する情報。</t>
   </si>
   <si>
     <t>JP Core Specimenリソースを参照する。</t>
@@ -872,7 +872,7 @@
     <t>この診断レポートの一部となるObservationに関する情報【詳細参照】</t>
   </si>
   <si>
-    <t>この診断レポートの一部となるObservationに関する情報</t>
+    <t>この診断レポートの一部となるObservationに関する情報。</t>
   </si>
   <si>
     <t>病理では未使用。</t>
@@ -897,10 +897,10 @@
     <t>診断レポートに関連づけれられたDICOM画像に関する情報【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートに関連づけれられたDICOM画像に関する情報</t>
-  </si>
-  <si>
-    <t>JP Core ImagingStudy Pathologyリソースを参照する。</t>
+    <t>診断レポートに関連づけれられたDICOM画像に関する情報。</t>
+  </si>
+  <si>
+    <t>JP Core ImagingStudy Pthologyリソースを参照する。</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target[classsCode=DGIMG, moodCode=EVN]</t>
@@ -920,7 +920,7 @@
     <t>診断レポートに関連づけられたメディアに関する情報【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートに関連づけられたメディアに関する情報</t>
+    <t>診断レポートに関連づけられたメディアに関する情報。</t>
   </si>
   <si>
     <t>主に、レポートに添付される画像を指す。</t>
@@ -984,10 +984,10 @@
     <t>メディアに関するコメント【詳細参照】</t>
   </si>
   <si>
-    <t>メディアに関するコメント</t>
-  </si>
-  <si>
-    <t>以下のいずれかを記載する。・参照画像としての添付されたイメージ・診断用スライドをスキャンしたイメージ</t>
+    <t>メディアに関するコメント。</t>
+  </si>
+  <si>
+    <t>以下のいずれかを記載する。参照画像としての添付されたイメージ、診断用スライドをスキャンしたイメージ。</t>
   </si>
   <si>
     <t>レポートのプロバイダーは、レポートに含まれる各画像についてコメントする必要があります。 / The provider of the report should make a comment about each image included in the report.</t>
@@ -1006,7 +1006,7 @@
     <t>メディアの参照先【詳細参照】</t>
   </si>
   <si>
-    <t>メディアの参照先</t>
+    <t>メディアの参照先。</t>
   </si>
   <si>
     <t>JP Core Media Pathologyリソースを参照する。</t>
@@ -1025,7 +1025,7 @@
     <t>総合診断に相当する要約結論【詳細参照】</t>
   </si>
   <si>
-    <t>総合診断に相当する要約結論</t>
+    <t>総合診断に相当する要約結論。</t>
   </si>
   <si>
     <t>テキストで可能な限り記載する。</t>
@@ -1046,7 +1046,7 @@
     <t>病理診断レポートの要約結論を表す1つ以上のコード【詳細参照】</t>
   </si>
   <si>
-    <t>病理診断レポートの要約結論を表す1つ以上のコード</t>
+    <t>病理診断レポートの要約結論を表す1つ以上のコード。</t>
   </si>
   <si>
     <t>腫瘍の場合はICD-O-3、腫瘍以外はICD-10、ICD-11の病名を設定する。ただし、運用上コード指定ができない場合、設定されなくてもよい。</t>
@@ -1071,7 +1071,7 @@
     <t>診断レポート本体【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポート本体</t>
+    <t>診断レポート本体。</t>
   </si>
   <si>
     <t>診断レポート本体をPDF形式やxml形式などで添付する（フォーマットは不問）。</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$44</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="397">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:51:50+00:00</t>
+    <t>2026-08-12T07:04:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>病理にて作成された診断レポート。</t>
+    <t>このプロファイルはDiagnosticReportリソースに対して、病理分野の診断レポートのデータを送受信するための制約と拡張を定めたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,7 +269,11 @@
 </t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする概要情報の表示に使用するのに適していません。たとえば、このリソースは、実験室の累積レポート形式や、シーケンスのための詳細な構造化されたレポート向けに設計されていません。 / This is intended to capture a single report and is not suitable for use in displaying summary information that covers multiple reports.  For example, this resource has not been designed for laboratory cumulative reporting formats nor detailed structured reports for sequencing.</t>
+    <t>病理にて作成された診断レポート。</t>
+  </si>
+  <si>
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -493,7 +497,7 @@
     <t>病理では標本番号（受付番号、病理番号）＋版数を指定する。</t>
   </si>
   <si>
-    <t>ソース研究所からのこのレポートについてクエリを作成する際に使用するidentifierを知る必要があります。 / Need to know what identifier to use when making queries about this report from the source laboratory, and for linking to the report outside FHIR context.</t>
+    <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -515,7 +519,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common)
 </t>
   </si>
   <si>
@@ -596,13 +600,7 @@
     <t>Value Set：JPCore_DiagnosticReport_Categoryの中から「LP7839-6」（Pathology（病理））を指定する。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -612,6 +610,208 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.system</t>
+  </si>
+  <si>
+    <t>カテゴリーコードシステムの識別URL</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.code</t>
+  </si>
+  <si>
+    <t>カテゴリーコード</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.display</t>
+  </si>
+  <si>
+    <t>カテゴリー表示名</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -630,10 +830,7 @@
     <t>Value Set：JPCore_DocumentCodeの中から適切な病理分野の報告書のコードを指定する。例：組織診は「11526-1」（病理検査報告書）、細胞診は「47526-9」（細胞診報告書）、剖検は「18743-5」（剖検報告書）を指定する。</t>
   </si>
   <si>
-    <t>診断レポートを説明するコード。 / Codes that describe Diagnostic Reports.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DocumentCodes_DiagnosticReport_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -799,7 +996,7 @@
     <t>レポートを確定した医師。</t>
   </si>
   <si>
-    <t>これは、必ずしもアトミックデータ項目または結果を解釈したエンティティのソースではありません。臨床報告に責任を負うのはエンティティです。 / This is not necessarily the source of the atomic data items or the entity that interpreted the results. It is the entity that takes responsibility for the clinical report.</t>
+    <t>必ずしも１項目データ単位のデータソースまたは結果を解釈した主体でなない。臨床レポートに責任をもつ主体のこと。</t>
   </si>
   <si>
     <t>結果についてクエリがある場合は、誰に連絡するかを知る必要があります。また、二次データ分析のためにレポートのソースを追跡する必要がある場合があります。 / Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
@@ -839,7 +1036,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Pathology)
 </t>
   </si>
   <si>
@@ -849,7 +1046,7 @@
     <t>この診断レポートの検体に関する情報。</t>
   </si>
   <si>
-    <t>JP Core Specimenリソースを参照する。</t>
+    <t>JP Core Specimen Pathologyリソースを参照する。</t>
   </si>
   <si>
     <t>レポートの基礎となる収集された標本に関する情報を報告できる必要があります。 / Need to be able to report information about the collected specimens on which the report is based.</t>
@@ -878,7 +1075,7 @@
     <t>病理では未使用。</t>
   </si>
   <si>
-    <t>個々の結果、または結果のグループが任意であるが意味のある結果のグループをサポートする必要があります。 / Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+    <t>個々の結果または結果のグループをサポートする必要がある。結果のグループ化は任意だが、意味がある場合にグループ化される。</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -890,7 +1087,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_ImagingStudy_Pathology)
 </t>
   </si>
   <si>
@@ -900,7 +1097,7 @@
     <t>診断レポートに関連づけれられたDICOM画像に関する情報。</t>
   </si>
   <si>
-    <t>JP Core ImagingStudy Pthologyリソースを参照する。</t>
+    <t>JP Core ImagingStudy Pathologyリソースを参照する。</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=COMP].target[classsCode=DGIMG, moodCode=EVN]</t>
@@ -926,7 +1123,7 @@
     <t>主に、レポートに添付される画像を指す。</t>
   </si>
   <si>
-    <t>多くの診断サービスには、サービスの一部としてレポートに画像が含まれています。 / Many diagnostic services include images in the report as part of their service.</t>
+    <t>多くの診断業務では提供情報の一部としてレポートに画像を含む。</t>
   </si>
   <si>
     <t>OBX?</t>
@@ -935,29 +1132,7 @@
     <t>DiagnosticReport.media.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DiagnosticReport.media.extension</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.media.modifierExtension</t>
@@ -999,7 +1174,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Pathology)
 </t>
   </si>
   <si>
@@ -1050,6 +1225,9 @@
   </si>
   <si>
     <t>腫瘍の場合はICD-O-3、腫瘍以外はICD-10、ICD-11の病名を設定する。ただし、運用上コード指定ができない場合、設定されなくてもよい。</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
@@ -1399,11 +1577,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.6171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.6171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1427,10 +1605,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.3515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1596,13 +1774,13 @@
         <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1664,16 +1842,16 @@
         <v>81</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>81</v>
@@ -1681,10 +1859,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1695,7 +1873,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>81</v>
@@ -1704,19 +1882,19 @@
         <v>81</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1766,13 +1944,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -1795,10 +1973,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1809,7 +1987,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>81</v>
@@ -1818,16 +1996,16 @@
         <v>81</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1878,19 +2056,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -1907,10 +2085,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1921,28 +2099,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1992,19 +2170,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2021,10 +2199,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2035,7 +2213,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2047,16 +2225,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2082,13 +2260,13 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>81</v>
@@ -2106,19 +2284,19 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2135,21 +2313,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2161,16 +2339,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2220,19 +2398,19 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>81</v>
@@ -2241,7 +2419,7 @@
         <v>81</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>81</v>
@@ -2249,14 +2427,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2275,16 +2453,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2334,7 +2512,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2355,7 +2533,7 @@
         <v>81</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>81</v>
@@ -2363,14 +2541,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2389,16 +2567,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2448,7 +2626,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2460,7 +2638,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -2469,7 +2647,7 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>81</v>
@@ -2477,14 +2655,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2497,25 +2675,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -2564,7 +2742,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2576,7 +2754,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2585,7 +2763,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -2593,14 +2771,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2616,22 +2794,22 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -2680,7 +2858,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2692,31 +2870,31 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2735,19 +2913,19 @@
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>81</v>
@@ -2796,7 +2974,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2808,16 +2986,16 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -2825,10 +3003,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2836,34 +3014,34 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>81</v>
@@ -2888,13 +3066,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -2912,43 +3090,43 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2964,19 +3142,19 @@
         <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3002,14 +3180,12 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y14" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
       </c>
@@ -3026,7 +3202,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3038,38 +3214,38 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
@@ -3078,20 +3254,18 @@
         <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3116,13 +3290,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3140,50 +3314,50 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3192,23 +3366,21 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>204</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3244,62 +3416,62 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>212</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -3308,22 +3480,22 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3372,50 +3544,50 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>81</v>
@@ -3424,23 +3596,19 @@
         <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
@@ -3488,50 +3656,50 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>236</v>
+        <v>135</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -3540,23 +3708,21 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -3592,62 +3758,62 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -3656,22 +3822,22 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>247</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3720,50 +3886,50 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -3772,23 +3938,21 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -3836,39 +4000,39 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3879,7 +4043,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -3888,22 +4052,20 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -3952,28 +4114,28 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -3981,21 +4143,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4004,22 +4166,20 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4068,28 +4228,28 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>275</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4097,10 +4257,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4111,7 +4271,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4120,21 +4280,23 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4182,28 +4344,28 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4211,21 +4373,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -4234,22 +4396,22 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>285</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4298,28 +4460,28 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4327,21 +4489,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -4350,18 +4512,20 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>292</v>
+        <v>182</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4386,13 +4550,11 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4410,50 +4572,50 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -4462,21 +4624,23 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>136</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4524,74 +4688,74 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>138</v>
+        <v>282</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>144</v>
+        <v>283</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -4640,50 +4804,50 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -4692,22 +4856,22 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="N29" t="s" s="2">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4756,50 +4920,50 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -4808,21 +4972,23 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -4870,50 +5036,50 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -4922,22 +5088,22 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -4986,43 +5152,43 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5038,21 +5204,23 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>181</v>
+        <v>311</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5076,13 +5244,13 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>330</v>
+        <v>81</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
@@ -5100,7 +5268,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5112,27 +5280,27 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5146,7 +5314,7 @@
         <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
@@ -5155,19 +5323,19 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5216,7 +5384,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5228,23 +5396,1287 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="P34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN33">
+  <autoFilter ref="A1:AN44">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5254,7 +6686,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI32">
+  <conditionalFormatting sqref="A2:AI43">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:04:31+00:00</t>
+    <t>2026-08-12T07:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:45:23+00:00</t>
+    <t>2026-08-12T12:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:14:47+00:00</t>
+    <t>2026-08-12T12:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="414">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T12:53:42+00:00</t>
+    <t>2026-08-12T13:21:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,16 +591,20 @@
 </t>
   </si>
   <si>
-    <t>診断レポートの分野を表すコード【詳細参照】</t>
-  </si>
-  <si>
-    <t>診断レポートの分野を表すコード。</t>
-  </si>
-  <si>
-    <t>Value Set：JPCore_DiagnosticReport_Categoryの中から「LP7839-6」（Pathology（病理））を指定する。</t>
+    <t>診断レポートを作成した臨床分野、部門、または診断サービス（心臓病学、生化学、血液学、放射線医学など）を分類するコード</t>
+  </si>
+  <si>
+    <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -644,9 +648,6 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -812,6 +813,63 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>診断レポートの分野を表すコード【詳細参照】</t>
+  </si>
+  <si>
+    <t>診断レポートの分野を表すコード。</t>
+  </si>
+  <si>
+    <t>Value Set：JPCore_DiagnosticReport_Categoryの中から「LP7839-6」（Pathology（病理））を指定する。</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP7839-6"/&gt;
+    &lt;display value="病理"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.system</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.text</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1577,10 +1635,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
@@ -3130,7 +3188,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>80</v>
@@ -3151,10 +3209,10 @@
         <v>183</v>
       </c>
       <c r="M14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3184,22 +3242,20 @@
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>81</v>
-      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>180</v>
@@ -3220,21 +3276,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3257,13 +3313,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3314,7 +3370,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3335,7 +3391,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3343,10 +3399,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3375,7 +3431,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>139</v>
@@ -3416,16 +3472,16 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>201</v>
@@ -3449,7 +3505,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3599,13 +3655,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3656,7 +3712,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3677,7 +3733,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3717,7 +3773,7 @@
         <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>139</v>
@@ -3758,16 +3814,16 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>201</v>
@@ -3791,7 +3847,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3941,7 +3997,7 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>221</v>
@@ -4169,7 +4225,7 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>234</v>
@@ -4399,7 +4455,7 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>249</v>
@@ -4492,11 +4548,13 @@
         <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="D26" t="s" s="2">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4535,7 +4593,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4550,11 +4608,11 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>185</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4572,13 +4630,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -4587,28 +4645,28 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>189</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>191</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4624,23 +4682,19 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -4688,7 +4742,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>195</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4700,38 +4754,38 @@
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>278</v>
+        <v>135</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -4740,23 +4794,21 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -4792,62 +4844,62 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -4859,19 +4911,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>206</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>207</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4920,13 +4972,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -4935,28 +4987,28 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>298</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>300</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4972,23 +5024,19 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>193</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5036,7 +5084,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5048,31 +5096,31 @@
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5088,23 +5136,21 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5140,19 +5186,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5164,38 +5210,38 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>196</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5207,19 +5253,19 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>214</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>214</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>323</v>
+        <v>215</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5268,13 +5314,13 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>217</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
@@ -5283,24 +5329,24 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>317</v>
+        <v>219</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5311,7 +5357,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5320,23 +5366,21 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>221</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>222</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5384,13 +5428,13 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>224</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
@@ -5402,10 +5446,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>331</v>
+        <v>225</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5413,21 +5457,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -5436,22 +5480,20 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>334</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>338</v>
+        <v>229</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5500,13 +5542,13 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>230</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
@@ -5518,10 +5560,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>339</v>
+        <v>231</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>232</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5529,10 +5571,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5543,7 +5585,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5552,21 +5594,21 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>342</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5614,13 +5656,13 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
@@ -5632,10 +5674,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>346</v>
+        <v>238</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5643,21 +5685,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>271</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -5669,19 +5711,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>349</v>
+        <v>240</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>350</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
+        <v>242</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>352</v>
+        <v>243</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>353</v>
+        <v>244</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5730,13 +5772,13 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
@@ -5748,10 +5790,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>354</v>
+        <v>246</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>340</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5759,10 +5801,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5782,19 +5824,23 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
       </c>
@@ -5842,7 +5888,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5854,16 +5900,16 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5871,21 +5917,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>135</v>
+        <v>274</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -5894,19 +5940,19 @@
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>197</v>
+        <v>276</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5932,13 +5978,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5956,74 +6000,74 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>195</v>
+        <v>281</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>81</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>285</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>359</v>
+        <v>286</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>139</v>
+        <v>288</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>145</v>
+        <v>289</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6072,43 +6116,43 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>133</v>
+        <v>292</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>81</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6124,22 +6168,22 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>297</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>365</v>
+        <v>299</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>366</v>
+        <v>300</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6188,7 +6232,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6203,32 +6247,32 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>81</v>
+        <v>301</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -6243,18 +6287,20 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6302,10 +6348,10 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>90</v>
@@ -6317,28 +6363,28 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>314</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>375</v>
+        <v>317</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6354,22 +6400,22 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>318</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>378</v>
+        <v>321</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>379</v>
+        <v>322</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6418,7 +6464,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6436,25 +6482,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6470,21 +6516,23 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>182</v>
+        <v>328</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6508,13 +6556,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6532,7 +6580,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6547,28 +6595,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>380</v>
+        <v>333</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>389</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6578,28 +6626,28 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K44" t="s" s="2">
-        <v>391</v>
+        <v>328</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>339</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>394</v>
+        <v>340</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>395</v>
+        <v>331</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6648,7 +6696,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6663,20 +6711,1400 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="M52" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="P54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN44">
+  <autoFilter ref="A1:AN56">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6686,7 +8114,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI43">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:21:20+00:00</t>
+    <t>2026-08-13T00:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:17:30+00:00</t>
+    <t>2026-08-13T00:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T00:49:15+00:00</t>
+    <t>2026-08-13T01:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:04:13+00:00</t>
+    <t>2026-08-13T01:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T01:37:50+00:00</t>
+    <t>2026-08-13T08:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:49:13+00:00</t>
+    <t>2026-08-13T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:00:31+00:00</t>
+    <t>2026-08-13T13:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:31:56+00:00</t>
+    <t>2026-08-13T23:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:21:35+00:00</t>
+    <t>2026-08-13T23:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-pathology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:54:59+00:00</t>
+    <t>2026-08-19T04:30:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
